--- a/Report of Foresty_20251127/林業署前後測結果/初階班/圖表_2025.xlsx
+++ b/Report of Foresty_20251127/林業署前後測結果/初階班/圖表_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R\test\Macaca-population-trend\Report of Foresty_2025\林業署前後測結果\初階班\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R\test\Macaca-population-trend\Report of Foresty_20251127\林業署前後測結果\初階班\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEE944F-EFD4-4B57-A1CB-E0031EFF2547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61337C8C-B74A-4D4E-996B-5693AEED21AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12840" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-12840" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DT" sheetId="1" r:id="rId1"/>
@@ -978,7 +978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -989,6 +989,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -16919,10 +16920,10 @@
       <c r="A2" t="s">
         <v>154</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="6">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -16930,10 +16931,10 @@
       <c r="A3" t="s">
         <v>155</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>-1</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>0.32</v>
       </c>
     </row>
@@ -16941,10 +16942,10 @@
       <c r="A4" t="s">
         <v>156</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="6">
         <v>2.73</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="6">
         <v>0.01</v>
       </c>
     </row>
@@ -16952,10 +16953,10 @@
       <c r="A5" t="s">
         <v>157</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="6">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6">
         <v>1</v>
       </c>
     </row>
@@ -16963,10 +16964,10 @@
       <c r="A6" t="s">
         <v>158</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="6">
         <v>1.96</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>0.06</v>
       </c>
     </row>
@@ -16974,10 +16975,10 @@
       <c r="A7" t="s">
         <v>159</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="6">
         <v>-1</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="6">
         <v>0.32</v>
       </c>
     </row>
@@ -16985,10 +16986,10 @@
       <c r="A8" t="s">
         <v>160</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="6">
         <v>-1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="6">
         <v>0.32</v>
       </c>
     </row>
@@ -16996,10 +16997,10 @@
       <c r="A9" t="s">
         <v>161</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="6">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="6">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -17007,10 +17008,10 @@
       <c r="A10" t="s">
         <v>162</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
         <v>0.32</v>
       </c>
     </row>
@@ -17018,10 +17019,10 @@
       <c r="A11" t="s">
         <v>163</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="6">
         <v>-1</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="6">
         <v>0.32</v>
       </c>
     </row>
@@ -17029,10 +17030,10 @@
       <c r="A12" t="s">
         <v>164</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
         <v>0.32</v>
       </c>
     </row>
@@ -17040,10 +17041,10 @@
       <c r="A13" t="s">
         <v>63</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="6">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="6">
         <v>0.26</v>
       </c>
     </row>
@@ -17051,10 +17052,10 @@
       <c r="A14" t="s">
         <v>165</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="6">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="6">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -17062,10 +17063,10 @@
       <c r="A15" t="s">
         <v>66</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="6">
         <v>3.36</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17073,10 +17074,10 @@
       <c r="A16" t="s">
         <v>166</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
+      <c r="B16" s="6">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6">
         <v>1</v>
       </c>
     </row>
@@ -17084,10 +17085,10 @@
       <c r="A17" t="s">
         <v>167</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="6">
         <v>3.67</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17095,10 +17096,10 @@
       <c r="A18" t="s">
         <v>168</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="6">
         <v>2.2200000000000002</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="6">
         <v>0.03</v>
       </c>
     </row>
@@ -17106,10 +17107,10 @@
       <c r="A19" t="s">
         <v>169</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="6">
         <v>1.86</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -17117,10 +17118,10 @@
       <c r="A20" t="s">
         <v>170</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="6">
         <v>4.05</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17128,10 +17129,10 @@
       <c r="A21" t="s">
         <v>171</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="6">
         <v>3.2</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17139,10 +17140,10 @@
       <c r="A22" t="s">
         <v>58</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="6">
         <v>3.2</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17150,10 +17151,10 @@
       <c r="A23" t="s">
         <v>172</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="6">
         <v>3.12</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17161,10 +17162,10 @@
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="6">
         <v>1.84</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -17172,10 +17173,10 @@
       <c r="A25" t="s">
         <v>173</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="6">
         <v>5.65</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17183,10 +17184,10 @@
       <c r="A26" t="s">
         <v>174</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="6">
         <v>4.8899999999999997</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17194,10 +17195,10 @@
       <c r="A27" t="s">
         <v>175</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="6">
         <v>6.3</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17205,10 +17206,10 @@
       <c r="A28" t="s">
         <v>176</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="6">
         <v>2.68</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="6">
         <v>0.01</v>
       </c>
     </row>
@@ -17216,10 +17217,10 @@
       <c r="A29" t="s">
         <v>177</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="6">
         <v>2.2400000000000002</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="6">
         <v>0.03</v>
       </c>
     </row>
@@ -17227,10 +17228,10 @@
       <c r="A30" t="s">
         <v>178</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="6">
         <v>4.6399999999999997</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17238,10 +17239,10 @@
       <c r="A31" t="s">
         <v>179</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="6">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="6">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -17249,10 +17250,10 @@
       <c r="A32" t="s">
         <v>47</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="6">
         <v>1.31</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="6">
         <v>0.2</v>
       </c>
     </row>
@@ -17260,10 +17261,10 @@
       <c r="A33" t="s">
         <v>48</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="6">
         <v>4.82</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17271,10 +17272,10 @@
       <c r="A34" t="s">
         <v>49</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="6">
         <v>8.39</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17282,10 +17283,10 @@
       <c r="A35" t="s">
         <v>46</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="6">
         <v>7.4</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="6">
         <v>0</v>
       </c>
     </row>
@@ -17293,10 +17294,10 @@
       <c r="A36" t="s">
         <v>50</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="6">
         <v>6.54</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="6">
         <v>0</v>
       </c>
     </row>

--- a/Report of Foresty_20251127/林業署前後測結果/初階班/圖表_2025.xlsx
+++ b/Report of Foresty_20251127/林業署前後測結果/初階班/圖表_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R\test\Macaca-population-trend\Report of Foresty_20251127\林業署前後測結果\初階班\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61337C8C-B74A-4D4E-996B-5693AEED21AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9F097A-FA61-43A7-A3A2-7AC0FA3301CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12840" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-12840" windowWidth="16440" windowHeight="28320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DT" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DT!$A$1:$AZ$81</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">總分!$E$2:$E$81</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">總分!$F$2:$F$81</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">總分!$E$2:$E$81</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">總分!$F$2:$F$81</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">總分!$E$2:$E$81</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">總分!$F$2:$F$81</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">總分!$F$2:$F$81</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">總分!$E$2:$E$81</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">總分!$F$2:$F$81</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">總分!$E$2:$E$81</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">總分!$F$2:$F$81</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">總分!$E$2:$E$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -986,10 +1001,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3185,10 +3200,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.12</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3198,7 +3213,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{75851FBB-1E4E-4D13-B7DC-233CB037BE33}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.13</cx:f>
               <cx:v>總分</cx:v>
             </cx:txData>
           </cx:tx>
@@ -4166,6 +4181,93 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>28574</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="文字方塊 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7985F565-79D1-B36B-1631-16F4F6C51B56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15878174" y="4962525"/>
+          <a:ext cx="1733551" cy="361950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>n =39, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" i="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>p</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> &lt; 0.001 </a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1800">
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -16920,10 +17022,10 @@
       <c r="A2" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -16931,10 +17033,10 @@
       <c r="A3" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>-1</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>0.32</v>
       </c>
     </row>
@@ -16942,10 +17044,10 @@
       <c r="A4" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2.73</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>0.01</v>
       </c>
     </row>
@@ -16953,10 +17055,10 @@
       <c r="A5" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="6">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
         <v>1</v>
       </c>
     </row>
@@ -16964,10 +17066,10 @@
       <c r="A6" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>1.96</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>0.06</v>
       </c>
     </row>
@@ -16975,10 +17077,10 @@
       <c r="A7" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>-1</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>0.32</v>
       </c>
     </row>
@@ -16986,10 +17088,10 @@
       <c r="A8" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>-1</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>0.32</v>
       </c>
     </row>
@@ -16997,10 +17099,10 @@
       <c r="A9" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -17008,10 +17110,10 @@
       <c r="A10" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
         <v>0.32</v>
       </c>
     </row>
@@ -17019,10 +17121,10 @@
       <c r="A11" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>-1</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>0.32</v>
       </c>
     </row>
@@ -17030,10 +17132,10 @@
       <c r="A12" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6">
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
         <v>0.32</v>
       </c>
     </row>
@@ -17041,10 +17143,10 @@
       <c r="A13" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>0.26</v>
       </c>
     </row>
@@ -17052,10 +17154,10 @@
       <c r="A14" t="s">
         <v>165</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -17063,10 +17165,10 @@
       <c r="A15" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>3.36</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17074,10 +17176,10 @@
       <c r="A16" t="s">
         <v>166</v>
       </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
         <v>1</v>
       </c>
     </row>
@@ -17085,10 +17187,10 @@
       <c r="A17" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>3.67</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17096,10 +17198,10 @@
       <c r="A18" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>2.2200000000000002</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>0.03</v>
       </c>
     </row>
@@ -17107,10 +17209,10 @@
       <c r="A19" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>1.86</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -17118,10 +17220,10 @@
       <c r="A20" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>4.05</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17129,10 +17231,10 @@
       <c r="A21" t="s">
         <v>171</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>3.2</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17140,10 +17242,10 @@
       <c r="A22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>3.2</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17151,10 +17253,10 @@
       <c r="A23" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>3.12</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17162,10 +17264,10 @@
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>1.84</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -17173,10 +17275,10 @@
       <c r="A25" t="s">
         <v>173</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>5.65</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17184,10 +17286,10 @@
       <c r="A26" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>4.8899999999999997</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17195,10 +17297,10 @@
       <c r="A27" t="s">
         <v>175</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>6.3</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17206,10 +17308,10 @@
       <c r="A28" t="s">
         <v>176</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>2.68</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>0.01</v>
       </c>
     </row>
@@ -17217,10 +17319,10 @@
       <c r="A29" t="s">
         <v>177</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>2.2400000000000002</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>0.03</v>
       </c>
     </row>
@@ -17228,10 +17330,10 @@
       <c r="A30" t="s">
         <v>178</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>4.6399999999999997</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17239,10 +17341,10 @@
       <c r="A31" t="s">
         <v>179</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>0.56999999999999995</v>
       </c>
     </row>
@@ -17250,10 +17352,10 @@
       <c r="A32" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>1.31</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>0.2</v>
       </c>
     </row>
@@ -17261,10 +17363,10 @@
       <c r="A33" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>4.82</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17272,10 +17374,10 @@
       <c r="A34" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="5">
         <v>8.39</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17283,10 +17385,10 @@
       <c r="A35" t="s">
         <v>46</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>7.4</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17294,10 +17396,10 @@
       <c r="A36" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>6.54</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>0</v>
       </c>
     </row>
@@ -17691,7 +17793,7 @@
       </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>204</v>
       </c>
       <c r="C5" t="s">
@@ -17789,7 +17891,7 @@
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>65</v>
       </c>
